--- a/论文/words.xlsx
+++ b/论文/words.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="417">
   <si>
     <t>Engineering Applications</t>
   </si>
@@ -92,7 +92,7 @@
     <t>intuitive</t>
   </si>
   <si>
-    <t>直觉的</t>
+    <t>直觉的,直观的</t>
   </si>
   <si>
     <t>coherence</t>
@@ -710,252 +710,255 @@
     <t>extensive</t>
   </si>
   <si>
+    <t>全面的,大量的</t>
+  </si>
+  <si>
+    <t>disorder</t>
+  </si>
+  <si>
+    <t>扰乱</t>
+  </si>
+  <si>
+    <t>disrupt</t>
+  </si>
+  <si>
+    <t>中断,扰乱</t>
+  </si>
+  <si>
+    <t>reformulate</t>
+  </si>
+  <si>
+    <t>重新表述</t>
+  </si>
+  <si>
+    <t>tunes</t>
+  </si>
+  <si>
+    <t>微调</t>
+  </si>
+  <si>
+    <t>metrics</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>further</t>
+  </si>
+  <si>
+    <t>更远的,进一步</t>
+  </si>
+  <si>
+    <t>unimodal</t>
+  </si>
+  <si>
+    <t>单模态</t>
+  </si>
+  <si>
+    <t>consistency</t>
+  </si>
+  <si>
+    <t>一致性</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>ethics statement</t>
+  </si>
+  <si>
+    <t>道德说明</t>
+  </si>
+  <si>
+    <t>proposed method</t>
+  </si>
+  <si>
+    <t>所提方法</t>
+  </si>
+  <si>
+    <t>multi-class</t>
+  </si>
+  <si>
+    <t>多类别</t>
+  </si>
+  <si>
+    <t>appealing</t>
+  </si>
+  <si>
+    <t>影响力</t>
+  </si>
+  <si>
+    <t>Acknowledgement</t>
+  </si>
+  <si>
+    <t>致谢</t>
+  </si>
+  <si>
+    <t>empathetic Companion</t>
+  </si>
+  <si>
+    <t>共情陪伴</t>
+  </si>
+  <si>
+    <t>fusion mechanism</t>
+  </si>
+  <si>
+    <t>融合机制</t>
+  </si>
+  <si>
+    <t>hinder</t>
+  </si>
+  <si>
+    <t>阻碍,制约</t>
+  </si>
+  <si>
+    <t>account for</t>
+  </si>
+  <si>
+    <t>解决,处理,考虑到</t>
+  </si>
+  <si>
+    <t>inherent</t>
+  </si>
+  <si>
+    <t>天然的,固有的</t>
+  </si>
+  <si>
+    <t>specific in conversation</t>
+  </si>
+  <si>
+    <t>对话中特有的</t>
+  </si>
+  <si>
+    <t>local cause query</t>
+  </si>
+  <si>
+    <t>局部原因查询</t>
+  </si>
+  <si>
+    <t>subsequently</t>
+  </si>
+  <si>
+    <t>随后</t>
+  </si>
+  <si>
+    <t>in the literature</t>
+  </si>
+  <si>
+    <t>在文献中</t>
+  </si>
+  <si>
+    <t>often embedded</t>
+  </si>
+  <si>
+    <t>总是蕴含着</t>
+  </si>
+  <si>
+    <t>nuanced</t>
+  </si>
+  <si>
+    <t>微妙地</t>
+  </si>
+  <si>
+    <t>uncover</t>
+  </si>
+  <si>
+    <t>揭露,发现</t>
+  </si>
+  <si>
+    <t>semantic insights</t>
+  </si>
+  <si>
+    <t>语义信息</t>
+  </si>
+  <si>
+    <t>in essence</t>
+  </si>
+  <si>
+    <t>从本质上</t>
+  </si>
+  <si>
+    <t>encompassing</t>
+  </si>
+  <si>
+    <t>包含,涵盖</t>
+  </si>
+  <si>
+    <t>conversational dialogue</t>
+  </si>
+  <si>
+    <t>口语对话/对话</t>
+  </si>
+  <si>
+    <t>text components</t>
+  </si>
+  <si>
+    <t>文本组件</t>
+  </si>
+  <si>
+    <t>linguistic cues</t>
+  </si>
+  <si>
+    <t>语言线索</t>
+  </si>
+  <si>
+    <t>convey</t>
+  </si>
+  <si>
+    <t>传达</t>
+  </si>
+  <si>
+    <t>encapsulate</t>
+  </si>
+  <si>
+    <t>概述、封装</t>
+  </si>
+  <si>
+    <t>tone</t>
+  </si>
+  <si>
+    <t>语气 说话时的整体情感色彩比如愤怒</t>
+  </si>
+  <si>
+    <t>intonation</t>
+  </si>
+  <si>
+    <t>语调 句子整体的音调起伏模式 陈述句下降</t>
+  </si>
+  <si>
+    <t>pitch</t>
+  </si>
+  <si>
+    <t>音高 声音的频率高低,高低音</t>
+  </si>
+  <si>
+    <t>holistic</t>
+  </si>
+  <si>
+    <t>整体的,全面的</t>
+  </si>
+  <si>
+    <t>complementary insights</t>
+  </si>
+  <si>
+    <t>互补洞察</t>
+  </si>
+  <si>
+    <t>spectrum</t>
+  </si>
+  <si>
+    <t>谱系</t>
+  </si>
+  <si>
+    <t>comprehensive</t>
+  </si>
+  <si>
     <t>全面的</t>
   </si>
   <si>
-    <t>disorder</t>
-  </si>
-  <si>
-    <t>扰乱</t>
-  </si>
-  <si>
-    <t>disrupt</t>
-  </si>
-  <si>
-    <t>中断,扰乱</t>
-  </si>
-  <si>
-    <t>reformulate</t>
-  </si>
-  <si>
-    <t>重新表述</t>
-  </si>
-  <si>
-    <t>tunes</t>
-  </si>
-  <si>
-    <t>微调</t>
-  </si>
-  <si>
-    <t>metrics</t>
-  </si>
-  <si>
-    <t>指标</t>
-  </si>
-  <si>
-    <t>further</t>
-  </si>
-  <si>
-    <t>更远的,进一步</t>
-  </si>
-  <si>
-    <t>unimodal</t>
-  </si>
-  <si>
-    <t>单模态</t>
-  </si>
-  <si>
-    <t>consistency</t>
-  </si>
-  <si>
-    <t>一致性</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>ethics statement</t>
-  </si>
-  <si>
-    <t>道德说明</t>
-  </si>
-  <si>
-    <t>proposed method</t>
-  </si>
-  <si>
-    <t>所提方法</t>
-  </si>
-  <si>
-    <t>multi-class</t>
-  </si>
-  <si>
-    <t>多类别</t>
-  </si>
-  <si>
-    <t>appealing</t>
-  </si>
-  <si>
-    <t>影响力</t>
-  </si>
-  <si>
-    <t>Acknowledgement</t>
-  </si>
-  <si>
-    <t>致谢</t>
-  </si>
-  <si>
-    <t>empathetic Companion</t>
-  </si>
-  <si>
-    <t>共情陪伴</t>
-  </si>
-  <si>
-    <t>fusion mechanism</t>
-  </si>
-  <si>
-    <t>融合机制</t>
-  </si>
-  <si>
-    <t>hinder</t>
-  </si>
-  <si>
-    <t>阻碍,制约</t>
-  </si>
-  <si>
-    <t>account for</t>
-  </si>
-  <si>
-    <t>解决,处理,考虑到</t>
-  </si>
-  <si>
-    <t>inherent</t>
-  </si>
-  <si>
-    <t>天然的,固有的</t>
-  </si>
-  <si>
-    <t>specific in conversation</t>
-  </si>
-  <si>
-    <t>对话中特有的</t>
-  </si>
-  <si>
-    <t>local cause query</t>
-  </si>
-  <si>
-    <t>局部原因查询</t>
-  </si>
-  <si>
-    <t>subsequently</t>
-  </si>
-  <si>
-    <t>随后</t>
-  </si>
-  <si>
-    <t>in the literature</t>
-  </si>
-  <si>
-    <t>在文献中</t>
-  </si>
-  <si>
-    <t>often embedded</t>
-  </si>
-  <si>
-    <t>总是蕴含着</t>
-  </si>
-  <si>
-    <t>nuanced</t>
-  </si>
-  <si>
-    <t>微妙地</t>
-  </si>
-  <si>
-    <t>uncover</t>
-  </si>
-  <si>
-    <t>揭露,发现</t>
-  </si>
-  <si>
-    <t>semantic insights</t>
-  </si>
-  <si>
-    <t>语义信息</t>
-  </si>
-  <si>
-    <t>in essence</t>
-  </si>
-  <si>
-    <t>从本质上</t>
-  </si>
-  <si>
-    <t>encompassing</t>
-  </si>
-  <si>
-    <t>包含,涵盖</t>
-  </si>
-  <si>
-    <t>conversational dialogue</t>
-  </si>
-  <si>
-    <t>口语对话/对话</t>
-  </si>
-  <si>
-    <t>text components</t>
-  </si>
-  <si>
-    <t>文本组件</t>
-  </si>
-  <si>
-    <t>linguistic cues</t>
-  </si>
-  <si>
-    <t>语言线索</t>
-  </si>
-  <si>
-    <t>convey</t>
-  </si>
-  <si>
-    <t>传达</t>
-  </si>
-  <si>
-    <t>encapsulate</t>
-  </si>
-  <si>
-    <t>概述、封装</t>
-  </si>
-  <si>
-    <t>tone</t>
-  </si>
-  <si>
-    <t>语气 说话时的整体情感色彩比如愤怒</t>
-  </si>
-  <si>
-    <t>intonation</t>
-  </si>
-  <si>
-    <t>语调 句子整体的音调起伏模式 陈述句下降</t>
-  </si>
-  <si>
-    <t>pitch</t>
-  </si>
-  <si>
-    <t>音高 声音的频率高低,高低音</t>
-  </si>
-  <si>
-    <t>holistic</t>
-  </si>
-  <si>
-    <t>整体的,全面的</t>
-  </si>
-  <si>
-    <t>complementary insights</t>
-  </si>
-  <si>
-    <t>互补洞察</t>
-  </si>
-  <si>
-    <t>spectrum</t>
-  </si>
-  <si>
-    <t>谱系</t>
-  </si>
-  <si>
-    <t>comprehensive</t>
-  </si>
-  <si>
     <t>this advancement</t>
   </si>
   <si>
@@ -966,6 +969,315 @@
   </si>
   <si>
     <t>创新</t>
+  </si>
+  <si>
+    <t>examining</t>
+  </si>
+  <si>
+    <t>审视,检查</t>
+  </si>
+  <si>
+    <t>identify</t>
+  </si>
+  <si>
+    <t>识别出</t>
+  </si>
+  <si>
+    <t>constitute</t>
+  </si>
+  <si>
+    <t>组成,构成</t>
+  </si>
+  <si>
+    <t>imperative</t>
+  </si>
+  <si>
+    <t>极其重要的</t>
+  </si>
+  <si>
+    <t>sophisicated</t>
+  </si>
+  <si>
+    <t>复杂的</t>
+  </si>
+  <si>
+    <t>suboptimal</t>
+  </si>
+  <si>
+    <t>次最优的</t>
+  </si>
+  <si>
+    <t>facilitating</t>
+  </si>
+  <si>
+    <t>使更容易,促进</t>
+  </si>
+  <si>
+    <t>consequently</t>
+  </si>
+  <si>
+    <t>因此,结果</t>
+  </si>
+  <si>
+    <t>aforementioned</t>
+  </si>
+  <si>
+    <t>上述的</t>
+  </si>
+  <si>
+    <t>correlated</t>
+  </si>
+  <si>
+    <t>被关联</t>
+  </si>
+  <si>
+    <t>global</t>
+  </si>
+  <si>
+    <t>全局</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>范围</t>
+  </si>
+  <si>
+    <t>in summary</t>
+  </si>
+  <si>
+    <t>总之,概况起来</t>
+  </si>
+  <si>
+    <t>attention module</t>
+  </si>
+  <si>
+    <t>注意力模块</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>约束</t>
+  </si>
+  <si>
+    <t>conduct</t>
+  </si>
+  <si>
+    <t>进行</t>
+  </si>
+  <si>
+    <t>remainder</t>
+  </si>
+  <si>
+    <t>剩余部分</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>回顾</t>
+  </si>
+  <si>
+    <t>elaboration</t>
+  </si>
+  <si>
+    <t>详细阐述</t>
+  </si>
+  <si>
+    <t>hyper-parameter</t>
+  </si>
+  <si>
+    <t>超参数</t>
+  </si>
+  <si>
+    <t>case study</t>
+  </si>
+  <si>
+    <t>案例研究</t>
+  </si>
+  <si>
+    <t>conclude</t>
+  </si>
+  <si>
+    <t>推断,总结</t>
+  </si>
+  <si>
+    <t>outline</t>
+  </si>
+  <si>
+    <t>v.概述 n.轮廓</t>
+  </si>
+  <si>
+    <t>critical</t>
+  </si>
+  <si>
+    <t>关键</t>
+  </si>
+  <si>
+    <t>integrate</t>
+  </si>
+  <si>
+    <t>robustness</t>
+  </si>
+  <si>
+    <t>鲁棒性</t>
+  </si>
+  <si>
+    <t>context construction</t>
+  </si>
+  <si>
+    <t>上下文结构</t>
+  </si>
+  <si>
+    <t>employ</t>
+  </si>
+  <si>
+    <t>采用</t>
+  </si>
+  <si>
+    <t>coined</t>
+  </si>
+  <si>
+    <t>创造</t>
+  </si>
+  <si>
+    <t>pre-specifying</t>
+  </si>
+  <si>
+    <t>预格式化,预指定</t>
+  </si>
+  <si>
+    <t>transition</t>
+  </si>
+  <si>
+    <t>转变</t>
+  </si>
+  <si>
+    <t>in light of</t>
+  </si>
+  <si>
+    <t>基于某种情况,鉴于</t>
+  </si>
+  <si>
+    <t>extant</t>
+  </si>
+  <si>
+    <t>现存的</t>
+  </si>
+  <si>
+    <t>note that</t>
+  </si>
+  <si>
+    <t>注意</t>
+  </si>
+  <si>
+    <t>in practice</t>
+  </si>
+  <si>
+    <t>在实践中</t>
+  </si>
+  <si>
+    <t>a given</t>
+  </si>
+  <si>
+    <t>给定</t>
+  </si>
+  <si>
+    <t>sequentially</t>
+  </si>
+  <si>
+    <t>继续地</t>
+  </si>
+  <si>
+    <t>subsection</t>
+  </si>
+  <si>
+    <t>分段,分片</t>
+  </si>
+  <si>
+    <t>corpus</t>
+  </si>
+  <si>
+    <t>语料库,全集</t>
+  </si>
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>前缀</t>
+  </si>
+  <si>
+    <t>submodule</t>
+  </si>
+  <si>
+    <t>子模块</t>
+  </si>
+  <si>
+    <t>For the sake of</t>
+  </si>
+  <si>
+    <t>出于...目的</t>
+  </si>
+  <si>
+    <t>brevity</t>
+  </si>
+  <si>
+    <t>简介,短暂</t>
+  </si>
+  <si>
+    <t>residual</t>
+  </si>
+  <si>
+    <t>残留的</t>
+  </si>
+  <si>
+    <t>generalization</t>
+  </si>
+  <si>
+    <t>概括,泛化</t>
+  </si>
+  <si>
+    <t>Feed forward Network</t>
+  </si>
+  <si>
+    <t>前倾网络</t>
+  </si>
+  <si>
+    <t>transformation</t>
+  </si>
+  <si>
+    <t>变化</t>
+  </si>
+  <si>
+    <t>sequently</t>
+  </si>
+  <si>
+    <t>依次</t>
+  </si>
+  <si>
+    <t>rectify</t>
+  </si>
+  <si>
+    <t>纠正</t>
+  </si>
+  <si>
+    <t>exploit</t>
+  </si>
+  <si>
+    <t>利用</t>
+  </si>
+  <si>
+    <t>Discrepancy</t>
+  </si>
+  <si>
+    <t>差异</t>
+  </si>
+  <si>
+    <t>bridging discrepancy</t>
+  </si>
+  <si>
+    <t>弥合差距</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2447,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:C157"/>
+  <dimension ref="B1:C209"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20.6388888888889" customWidth="1"/>
@@ -3380,23 +3692,439 @@
         <v>308</v>
       </c>
       <c r="C155" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
     </row>
     <row r="156" spans="2:3">
       <c r="B156" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C156" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="157" spans="2:3">
       <c r="B157" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C157" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158" spans="2:3">
+      <c r="B158" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159" spans="2:3">
+      <c r="B159" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160" spans="2:3">
+      <c r="B160" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3">
+      <c r="B161" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="162" spans="2:3">
+      <c r="B162" t="s">
+        <v>322</v>
+      </c>
+      <c r="C162" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3">
+      <c r="B163" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164" spans="2:3">
+      <c r="B164" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165" spans="2:3">
+      <c r="B165" t="s">
+        <v>328</v>
+      </c>
+      <c r="C165" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="166" spans="2:3">
+      <c r="B166" t="s">
+        <v>330</v>
+      </c>
+      <c r="C166" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3">
+      <c r="B167" t="s">
+        <v>332</v>
+      </c>
+      <c r="C167" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="168" spans="2:3">
+      <c r="B168" t="s">
+        <v>334</v>
+      </c>
+      <c r="C168" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169" spans="2:3">
+      <c r="B169" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="170" spans="2:3">
+      <c r="B170" t="s">
+        <v>338</v>
+      </c>
+      <c r="C170" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="171" spans="2:3">
+      <c r="B171" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="172" spans="2:3">
+      <c r="B172" t="s">
+        <v>342</v>
+      </c>
+      <c r="C172" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="173" spans="2:3">
+      <c r="B173" t="s">
+        <v>344</v>
+      </c>
+      <c r="C173" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3">
+      <c r="B174" t="s">
+        <v>346</v>
+      </c>
+      <c r="C174" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="175" spans="2:3">
+      <c r="B175" t="s">
+        <v>348</v>
+      </c>
+      <c r="C175" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="176" spans="2:3">
+      <c r="B176" t="s">
+        <v>350</v>
+      </c>
+      <c r="C176" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3">
+      <c r="B177" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3">
+      <c r="B178" t="s">
+        <v>354</v>
+      </c>
+      <c r="C178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3">
+      <c r="B179" t="s">
+        <v>356</v>
+      </c>
+      <c r="C179" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3">
+      <c r="B180" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="181" spans="2:3">
+      <c r="B181" t="s">
+        <v>360</v>
+      </c>
+      <c r="C181" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3">
+      <c r="B182" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3">
+      <c r="B183" t="s">
+        <v>363</v>
+      </c>
+      <c r="C183" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3">
+      <c r="B184" t="s">
+        <v>365</v>
+      </c>
+      <c r="C184" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3">
+      <c r="B185" t="s">
+        <v>367</v>
+      </c>
+      <c r="C185" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3">
+      <c r="B186" t="s">
+        <v>369</v>
+      </c>
+      <c r="C186" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3">
+      <c r="B187" t="s">
+        <v>371</v>
+      </c>
+      <c r="C187" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="188" spans="2:3">
+      <c r="B188" t="s">
+        <v>373</v>
+      </c>
+      <c r="C188" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3">
+      <c r="B189" t="s">
+        <v>375</v>
+      </c>
+      <c r="C189" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3">
+      <c r="B190" t="s">
+        <v>377</v>
+      </c>
+      <c r="C190" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3">
+      <c r="B191" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3">
+      <c r="B192" t="s">
+        <v>381</v>
+      </c>
+      <c r="C192" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3">
+      <c r="B193" t="s">
+        <v>383</v>
+      </c>
+      <c r="C193" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3">
+      <c r="B194" t="s">
+        <v>385</v>
+      </c>
+      <c r="C194" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3">
+      <c r="B195" t="s">
+        <v>387</v>
+      </c>
+      <c r="C195" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3">
+      <c r="B196" t="s">
+        <v>389</v>
+      </c>
+      <c r="C196" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3">
+      <c r="B197" t="s">
+        <v>391</v>
+      </c>
+      <c r="C197" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3">
+      <c r="B198" t="s">
+        <v>393</v>
+      </c>
+      <c r="C198" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3">
+      <c r="B199" t="s">
+        <v>395</v>
+      </c>
+      <c r="C199" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3">
+      <c r="B200" t="s">
+        <v>397</v>
+      </c>
+      <c r="C200" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3">
+      <c r="B201" t="s">
+        <v>399</v>
+      </c>
+      <c r="C201" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="202" spans="2:3">
+      <c r="B202" t="s">
+        <v>401</v>
+      </c>
+      <c r="C202" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3">
+      <c r="B203" t="s">
+        <v>403</v>
+      </c>
+      <c r="C203" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3">
+      <c r="B204" t="s">
+        <v>405</v>
+      </c>
+      <c r="C204" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3">
+      <c r="B205" t="s">
+        <v>407</v>
+      </c>
+      <c r="C205" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3">
+      <c r="B206" t="s">
+        <v>409</v>
+      </c>
+      <c r="C206" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3">
+      <c r="B207" t="s">
+        <v>411</v>
+      </c>
+      <c r="C207" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3">
+      <c r="B208" t="s">
+        <v>413</v>
+      </c>
+      <c r="C208" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="209" spans="2:3">
+      <c r="B209" t="s">
+        <v>415</v>
+      </c>
+      <c r="C209" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/论文/words.xlsx
+++ b/论文/words.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai notebook\论文\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
@@ -27,7 +32,502 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="518">
+  <si>
+    <t>a given</t>
+  </si>
+  <si>
+    <t>给定</t>
+  </si>
+  <si>
+    <t>ablation study</t>
+  </si>
+  <si>
+    <t>消融实验</t>
+  </si>
+  <si>
+    <t>account for</t>
+  </si>
+  <si>
+    <t>解决,处理,考虑到</t>
+  </si>
+  <si>
+    <t>Acknowledgement</t>
+  </si>
+  <si>
+    <t>致谢</t>
+  </si>
+  <si>
+    <t>acoustic</t>
+  </si>
+  <si>
+    <t>声音的</t>
+  </si>
+  <si>
+    <t>adaptive</t>
+  </si>
+  <si>
+    <t>适应的,有能力</t>
+  </si>
+  <si>
+    <t>adaptive hybrid</t>
+  </si>
+  <si>
+    <t>自适应融合</t>
+  </si>
+  <si>
+    <t>adjacent ao G sen te</t>
+  </si>
+  <si>
+    <t>邻近的</t>
+  </si>
+  <si>
+    <t>affect or feelings</t>
+  </si>
+  <si>
+    <t>情感或感受</t>
+  </si>
+  <si>
+    <t>aforementioned</t>
+  </si>
+  <si>
+    <t>上述的</t>
+  </si>
+  <si>
+    <t>aggregation</t>
+  </si>
+  <si>
+    <t>聚集,集合</t>
+  </si>
+  <si>
+    <t>alignment</t>
+  </si>
+  <si>
+    <t>对齐</t>
+  </si>
+  <si>
+    <t>annotated labels</t>
+  </si>
+  <si>
+    <t>带注释的标签</t>
+  </si>
+  <si>
+    <t>appealing</t>
+  </si>
+  <si>
+    <t>影响力</t>
+  </si>
+  <si>
+    <t>appendix</t>
+  </si>
+  <si>
+    <t>附录</t>
+  </si>
+  <si>
+    <t>arbitrary</t>
+  </si>
+  <si>
+    <t>任意</t>
+  </si>
+  <si>
+    <t>attention module</t>
+  </si>
+  <si>
+    <t>注意力模块</t>
+  </si>
+  <si>
+    <t>augment</t>
+  </si>
+  <si>
+    <t>v.增强</t>
+  </si>
+  <si>
+    <t>auto-regressive</t>
+  </si>
+  <si>
+    <t>自回归</t>
+  </si>
+  <si>
+    <t>Auxiliary</t>
+  </si>
+  <si>
+    <t>辅助</t>
+  </si>
+  <si>
+    <t>backbone</t>
+  </si>
+  <si>
+    <t>脊梁,基础</t>
+  </si>
+  <si>
+    <t>benchmark datasets</t>
+  </si>
+  <si>
+    <t>基准数据集</t>
+  </si>
+  <si>
+    <t>brevity</t>
+  </si>
+  <si>
+    <t>简介,短暂</t>
+  </si>
+  <si>
+    <t>bridging discrepancy</t>
+  </si>
+  <si>
+    <t>弥合差距</t>
+  </si>
+  <si>
+    <t>by a large margin</t>
+  </si>
+  <si>
+    <t>显著优势</t>
+  </si>
+  <si>
+    <t>case study</t>
+  </si>
+  <si>
+    <t>案例研究</t>
+  </si>
+  <si>
+    <t>Casual</t>
+  </si>
+  <si>
+    <t>因果</t>
+  </si>
+  <si>
+    <t>casual nature</t>
+  </si>
+  <si>
+    <t>因果本质</t>
+  </si>
+  <si>
+    <t>Casuality</t>
+  </si>
+  <si>
+    <t>因果关系</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>cause</t>
+  </si>
+  <si>
+    <t>n.原因,理由</t>
+  </si>
+  <si>
+    <t>coherence</t>
+  </si>
+  <si>
+    <t>连贯性,条理性</t>
+  </si>
+  <si>
+    <t>coined</t>
+  </si>
+  <si>
+    <t>创造</t>
+  </si>
+  <si>
+    <t>comparable</t>
+  </si>
+  <si>
+    <t>相当的</t>
+  </si>
+  <si>
+    <t>complementary insights</t>
+  </si>
+  <si>
+    <t>互补洞察</t>
+  </si>
+  <si>
+    <t>Complementary knowledge</t>
+  </si>
+  <si>
+    <t>互补知识</t>
+  </si>
+  <si>
+    <t>comprehensive</t>
+  </si>
+  <si>
+    <t>全面的</t>
+  </si>
+  <si>
+    <t>comprehensive evaluation</t>
+  </si>
+  <si>
+    <t>n.全面评估</t>
+  </si>
+  <si>
+    <t>comprise</t>
+  </si>
+  <si>
+    <t>包含,涵盖</t>
+  </si>
+  <si>
+    <t>computer vision</t>
+  </si>
+  <si>
+    <t>计算机视觉</t>
+  </si>
+  <si>
+    <t>concatenation</t>
+  </si>
+  <si>
+    <t>拼接</t>
+  </si>
+  <si>
+    <t>conclude</t>
+  </si>
+  <si>
+    <t>推断,总结</t>
+  </si>
+  <si>
+    <t>Concretely</t>
+  </si>
+  <si>
+    <t>具体的</t>
+  </si>
+  <si>
+    <t>conduct</t>
+  </si>
+  <si>
+    <t>进行</t>
+  </si>
+  <si>
+    <t>consequently</t>
+  </si>
+  <si>
+    <t>因此,结果</t>
+  </si>
+  <si>
+    <t>consistency</t>
+  </si>
+  <si>
+    <t>一致性</t>
+  </si>
+  <si>
+    <t>consistent</t>
+  </si>
+  <si>
+    <t>一致的</t>
+  </si>
+  <si>
+    <t>constitute</t>
+  </si>
+  <si>
+    <t>组成,构成</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>约束</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>Content list</t>
+  </si>
+  <si>
+    <t>目录列表,文件夹</t>
+  </si>
+  <si>
+    <t>context</t>
+  </si>
+  <si>
+    <t>上下文,背景</t>
+  </si>
+  <si>
+    <t>context construction</t>
+  </si>
+  <si>
+    <t>上下文结构</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>连续</t>
+  </si>
+  <si>
+    <t>converge on</t>
+  </si>
+  <si>
+    <t>聚集在</t>
+  </si>
+  <si>
+    <t>convergency</t>
+  </si>
+  <si>
+    <t>收敛性 verg弯曲,一起弯曲</t>
+  </si>
+  <si>
+    <t>conversational dialogue</t>
+  </si>
+  <si>
+    <t>口语对话/对话</t>
+  </si>
+  <si>
+    <t>convey</t>
+  </si>
+  <si>
+    <t>传达</t>
+  </si>
+  <si>
+    <t>corpus</t>
+  </si>
+  <si>
+    <t>语料库,全集</t>
+  </si>
+  <si>
+    <t>correlated</t>
+  </si>
+  <si>
+    <t>被关联</t>
+  </si>
+  <si>
+    <t>critical</t>
+  </si>
+  <si>
+    <t>关键</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>v.衰减</t>
+  </si>
+  <si>
+    <t>decision-making</t>
+  </si>
+  <si>
+    <t>决策能力</t>
+  </si>
+  <si>
+    <t>denote...respectively</t>
+  </si>
+  <si>
+    <t>分别表示</t>
+  </si>
+  <si>
+    <t>dense variants</t>
+  </si>
+  <si>
+    <t>密集变体</t>
+  </si>
+  <si>
+    <t>detect</t>
+  </si>
+  <si>
+    <t>查明,探查</t>
+  </si>
+  <si>
+    <t>dialog</t>
+  </si>
+  <si>
+    <t>对话</t>
+  </si>
+  <si>
+    <t>Discrepancy</t>
+  </si>
+  <si>
+    <t>差异</t>
+  </si>
+  <si>
+    <t>Discrete</t>
+  </si>
+  <si>
+    <t>离散</t>
+  </si>
+  <si>
+    <t>disorder</t>
+  </si>
+  <si>
+    <t>扰乱</t>
+  </si>
+  <si>
+    <t>disrupt</t>
+  </si>
+  <si>
+    <t>中断,扰乱</t>
+  </si>
+  <si>
+    <t>distribution</t>
+  </si>
+  <si>
+    <t>分布</t>
+  </si>
+  <si>
+    <t>dynamic</t>
+  </si>
+  <si>
+    <t>动态的,充满活力的 活力</t>
+  </si>
+  <si>
+    <t>elaboration</t>
+  </si>
+  <si>
+    <t>详细阐述</t>
+  </si>
+  <si>
+    <t>emotion and sentiment</t>
+  </si>
+  <si>
+    <t>情感和情绪</t>
+  </si>
+  <si>
+    <t>emotion specific representation</t>
+  </si>
+  <si>
+    <t>情感特定表征,某个句子整体情感向量</t>
+  </si>
+  <si>
+    <t>empathetic</t>
+  </si>
+  <si>
+    <t>同感</t>
+  </si>
+  <si>
+    <t>empathetic Companion</t>
+  </si>
+  <si>
+    <t>共情陪伴</t>
+  </si>
+  <si>
+    <t>employ</t>
+  </si>
+  <si>
+    <t>采用</t>
+  </si>
+  <si>
+    <t>enable</t>
+  </si>
+  <si>
+    <t>使实现</t>
+  </si>
+  <si>
+    <t>encapsulate</t>
+  </si>
+  <si>
+    <t>概述、封装</t>
+  </si>
+  <si>
+    <t>encompassing</t>
+  </si>
+  <si>
+    <t>end to end</t>
+  </si>
+  <si>
+    <t>端到端</t>
+  </si>
   <si>
     <t>Engineering Applications</t>
   </si>
@@ -35,10 +535,168 @@
     <t>工程应用</t>
   </si>
   <si>
-    <t>Content list</t>
-  </si>
-  <si>
-    <t>目录列表,文件夹</t>
+    <t>ethics statement</t>
+  </si>
+  <si>
+    <t>道德说明</t>
+  </si>
+  <si>
+    <t>evolve into</t>
+  </si>
+  <si>
+    <t>逐渐演变成</t>
+  </si>
+  <si>
+    <t>examining</t>
+  </si>
+  <si>
+    <t>审视,检查</t>
+  </si>
+  <si>
+    <t>excel in</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方面表现出色</t>
+    </r>
+  </si>
+  <si>
+    <t>Explicit</t>
+  </si>
+  <si>
+    <t>显式</t>
+  </si>
+  <si>
+    <t>exploit</t>
+  </si>
+  <si>
+    <t>利用</t>
+  </si>
+  <si>
+    <t>extant</t>
+  </si>
+  <si>
+    <t>现存的</t>
+  </si>
+  <si>
+    <t>extensive</t>
+  </si>
+  <si>
+    <t>全面的,大量的</t>
+  </si>
+  <si>
+    <t>extensively study</t>
+  </si>
+  <si>
+    <t>广泛研究</t>
+  </si>
+  <si>
+    <t>facilitating</t>
+  </si>
+  <si>
+    <t>使更容易,促进</t>
+  </si>
+  <si>
+    <t>Feed forward Network</t>
+  </si>
+  <si>
+    <t>前倾网络</t>
+  </si>
+  <si>
+    <t>Few-shot</t>
+  </si>
+  <si>
+    <t>少样本</t>
+  </si>
+  <si>
+    <t>For the sake of</t>
+  </si>
+  <si>
+    <t>出于...目的</t>
+  </si>
+  <si>
+    <t>framework</t>
+  </si>
+  <si>
+    <t>框架</t>
+  </si>
+  <si>
+    <t>further</t>
+  </si>
+  <si>
+    <t>更远的,进一步</t>
+  </si>
+  <si>
+    <t>further demostrating</t>
+  </si>
+  <si>
+    <t>进一步证明</t>
+  </si>
+  <si>
+    <t>fusion</t>
+  </si>
+  <si>
+    <t>融合</t>
+  </si>
+  <si>
+    <t>fusion mechanism</t>
+  </si>
+  <si>
+    <t>融合机制</t>
+  </si>
+  <si>
+    <t>generalization</t>
+  </si>
+  <si>
+    <t>概括,泛化</t>
+  </si>
+  <si>
+    <t>generate</t>
+  </si>
+  <si>
+    <t>生成</t>
+  </si>
+  <si>
+    <t>generation</t>
+  </si>
+  <si>
+    <t>生成,后代</t>
+  </si>
+  <si>
+    <t>Given</t>
+  </si>
+  <si>
+    <t>给定,对于</t>
+  </si>
+  <si>
+    <t>global</t>
+  </si>
+  <si>
+    <t>全局</t>
   </si>
   <si>
     <t>Graph neural networks</t>
@@ -47,22 +705,763 @@
     <t>图神经网络</t>
   </si>
   <si>
+    <t>Grouding</t>
+  </si>
+  <si>
+    <t>关联/接地/对齐</t>
+  </si>
+  <si>
+    <t>heterogeneous</t>
+  </si>
+  <si>
+    <t>异质性</t>
+  </si>
+  <si>
+    <t>hierarchical</t>
+  </si>
+  <si>
+    <t>分层的 Hier神圣的,arch统治者</t>
+  </si>
+  <si>
+    <t>hinder</t>
+  </si>
+  <si>
+    <t>阻碍,制约</t>
+  </si>
+  <si>
+    <t>holistic</t>
+  </si>
+  <si>
+    <t>整体的,全面的</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>首页</t>
+  </si>
+  <si>
+    <t>hyper-parameter</t>
+  </si>
+  <si>
+    <t>超参数</t>
+  </si>
+  <si>
+    <t>identify</t>
+  </si>
+  <si>
+    <t>识别出</t>
+  </si>
+  <si>
+    <t>illustrate</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>illustration</t>
+  </si>
+  <si>
+    <t>示意图,图解</t>
+  </si>
+  <si>
+    <t>imperative</t>
+  </si>
+  <si>
+    <t>极其重要的</t>
+  </si>
+  <si>
+    <t>implements</t>
+  </si>
+  <si>
+    <t>实现</t>
+  </si>
+  <si>
+    <t>implicit</t>
+  </si>
+  <si>
+    <t>隐式</t>
+  </si>
+  <si>
+    <t>imputation</t>
+  </si>
+  <si>
+    <t>n.补全</t>
+  </si>
+  <si>
+    <t>in essence</t>
+  </si>
+  <si>
+    <t>从本质上</t>
+  </si>
+  <si>
+    <t>in light of</t>
+  </si>
+  <si>
+    <t>基于某种情况,鉴于</t>
+  </si>
+  <si>
+    <t>in practice</t>
+  </si>
+  <si>
+    <t>在实践中</t>
+  </si>
+  <si>
+    <t>in summary</t>
+  </si>
+  <si>
+    <t>总之,概况起来</t>
+  </si>
+  <si>
+    <t>in the literature</t>
+  </si>
+  <si>
+    <t>在文献中</t>
+  </si>
+  <si>
+    <t>incorporate</t>
+  </si>
+  <si>
+    <t>包含,使并入</t>
+  </si>
+  <si>
+    <t>indicate</t>
+  </si>
+  <si>
+    <t>显示/表明，指明/验证</t>
+  </si>
+  <si>
+    <t>inference</t>
+  </si>
+  <si>
+    <t>推理</t>
+  </si>
+  <si>
+    <t>inherent</t>
+  </si>
+  <si>
+    <t>天然的,固有的</t>
+  </si>
+  <si>
+    <t>innovative</t>
+  </si>
+  <si>
+    <t>创新</t>
+  </si>
+  <si>
+    <t>integrate</t>
+  </si>
+  <si>
+    <t>intentions</t>
+  </si>
+  <si>
+    <t>意图</t>
+  </si>
+  <si>
+    <t>inter</t>
+  </si>
+  <si>
+    <t>跨层</t>
+  </si>
+  <si>
+    <t>interdependent</t>
+  </si>
+  <si>
+    <t>相互依赖的</t>
+  </si>
+  <si>
+    <t>inter-modality</t>
+  </si>
+  <si>
+    <t>模型间</t>
+  </si>
+  <si>
+    <t>intonation</t>
+  </si>
+  <si>
+    <t>语调 句子整体的音调起伏模式 陈述句下降</t>
+  </si>
+  <si>
+    <t>intra</t>
+  </si>
+  <si>
+    <t>层内</t>
+  </si>
+  <si>
     <t>introduce</t>
   </si>
   <si>
     <t>引入,介绍</t>
   </si>
   <si>
-    <t>dynamic</t>
-  </si>
-  <si>
-    <t>动态的,充满活力的 活力</t>
-  </si>
-  <si>
-    <t>Few-shot</t>
-  </si>
-  <si>
-    <t>少样本</t>
+    <t>intuitive</t>
+  </si>
+  <si>
+    <t>直觉的,直观的</t>
+  </si>
+  <si>
+    <t>is built on</t>
+  </si>
+  <si>
+    <t>基于</t>
+  </si>
+  <si>
+    <t>jointly training</t>
+  </si>
+  <si>
+    <t>联合训练</t>
+  </si>
+  <si>
+    <t>Language model</t>
+  </si>
+  <si>
+    <t>语言模型</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>层</t>
+  </si>
+  <si>
+    <t>learned representations</t>
+  </si>
+  <si>
+    <t>习得表征</t>
+  </si>
+  <si>
+    <t>leverage</t>
+  </si>
+  <si>
+    <t>充分利用</t>
+  </si>
+  <si>
+    <t>lie in</t>
+  </si>
+  <si>
+    <t>在于</t>
+  </si>
+  <si>
+    <t>linguistic cues</t>
+  </si>
+  <si>
+    <t>语言线索</t>
+  </si>
+  <si>
+    <t>local cause query</t>
+  </si>
+  <si>
+    <t>局部原因查询</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>人工,手工</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>掩码</t>
+  </si>
+  <si>
+    <t>masked reconstruction</t>
+  </si>
+  <si>
+    <t>掩码重建</t>
+  </si>
+  <si>
+    <t>Methodology</t>
+  </si>
+  <si>
+    <t>方法论</t>
+  </si>
+  <si>
+    <t>metrics</t>
+  </si>
+  <si>
+    <t>指标</t>
+  </si>
+  <si>
+    <t>minimalist</t>
+  </si>
+  <si>
+    <t>极简</t>
+  </si>
+  <si>
+    <t>modal fusion representations</t>
+  </si>
+  <si>
+    <t>模型融合表征</t>
+  </si>
+  <si>
+    <t>modality-specific featuers</t>
+  </si>
+  <si>
+    <t>模态特定特征</t>
+  </si>
+  <si>
+    <t>model effect</t>
+  </si>
+  <si>
+    <t>模型影响</t>
+  </si>
+  <si>
+    <t>model fine-tuning</t>
+  </si>
+  <si>
+    <t>模型微调</t>
+  </si>
+  <si>
+    <t>modelling</t>
+  </si>
+  <si>
+    <t>建模</t>
+  </si>
+  <si>
+    <t>multi-class</t>
+  </si>
+  <si>
+    <t>多类别</t>
+  </si>
+  <si>
+    <t>multi-party</t>
+  </si>
+  <si>
+    <t>多方</t>
+  </si>
+  <si>
+    <t>multi-turn</t>
+  </si>
+  <si>
+    <t>多轮对话</t>
+  </si>
+  <si>
+    <t>mutually influential</t>
+  </si>
+  <si>
+    <t>相互影响</t>
+  </si>
+  <si>
+    <t>necessitate</t>
+  </si>
+  <si>
+    <t>V.需要  nesaise tei te</t>
+  </si>
+  <si>
+    <t>Normalization</t>
+  </si>
+  <si>
+    <t>规划化</t>
+  </si>
+  <si>
+    <t>note that</t>
+  </si>
+  <si>
+    <t>注意</t>
+  </si>
+  <si>
+    <t>nuanced</t>
+  </si>
+  <si>
+    <t>微妙地</t>
+  </si>
+  <si>
+    <t>numerical sequential vectors</t>
+  </si>
+  <si>
+    <t>数值连续向量</t>
+  </si>
+  <si>
+    <t>often embedded</t>
+  </si>
+  <si>
+    <t>总是蕴含着</t>
+  </si>
+  <si>
+    <t>operation</t>
+  </si>
+  <si>
+    <t>操作,设计</t>
+  </si>
+  <si>
+    <t>outline</t>
+  </si>
+  <si>
+    <t>v.概述 n.轮廓</t>
+  </si>
+  <si>
+    <t>outperfoms</t>
+  </si>
+  <si>
+    <t>胜过</t>
+  </si>
+  <si>
+    <t>overlook</t>
+  </si>
+  <si>
+    <t>忽略</t>
+  </si>
+  <si>
+    <t>paradigm</t>
+  </si>
+  <si>
+    <t>范式</t>
+  </si>
+  <si>
+    <t>pipeline</t>
+  </si>
+  <si>
+    <t>流程,输送管道</t>
+  </si>
+  <si>
+    <t>pitch</t>
+  </si>
+  <si>
+    <t>音高 声音的频率高低,高低音</t>
+  </si>
+  <si>
+    <t>posses</t>
+  </si>
+  <si>
+    <t>v.具备,具有</t>
+  </si>
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>前缀</t>
+  </si>
+  <si>
+    <t>pre-specifying</t>
+  </si>
+  <si>
+    <t>预格式化,预指定</t>
+  </si>
+  <si>
+    <t>pre-trained foundation</t>
+  </si>
+  <si>
+    <t>预训练基础</t>
+  </si>
+  <si>
+    <t>probe</t>
+  </si>
+  <si>
+    <t>探查</t>
+  </si>
+  <si>
+    <t>processed</t>
+  </si>
+  <si>
+    <t>处理</t>
+  </si>
+  <si>
+    <t>projected</t>
+  </si>
+  <si>
+    <t>v.投影,投掷</t>
+  </si>
+  <si>
+    <t>promising</t>
+  </si>
+  <si>
+    <t>前景广阔</t>
+  </si>
+  <si>
+    <t>prompts</t>
+  </si>
+  <si>
+    <t>提示词</t>
+  </si>
+  <si>
+    <t>proposed method</t>
+  </si>
+  <si>
+    <t>所提方法</t>
+  </si>
+  <si>
+    <t>prototype</t>
+  </si>
+  <si>
+    <t>n.原型 purou te tai pu</t>
+  </si>
+  <si>
+    <t>raw acoustic input</t>
+  </si>
+  <si>
+    <t>原始音频输入</t>
+  </si>
+  <si>
+    <t>reading comprehension</t>
+  </si>
+  <si>
+    <t>阅读理解</t>
+  </si>
+  <si>
+    <t>real groud</t>
+  </si>
+  <si>
+    <t>真实答案下</t>
+  </si>
+  <si>
+    <t>recognition</t>
+  </si>
+  <si>
+    <t>n.识别,承认</t>
+  </si>
+  <si>
+    <t>rectify</t>
+  </si>
+  <si>
+    <t>纠正</t>
+  </si>
+  <si>
+    <t>reductions</t>
+  </si>
+  <si>
+    <t>减少</t>
+  </si>
+  <si>
+    <t>reformulate</t>
+  </si>
+  <si>
+    <t>重新表述</t>
+  </si>
+  <si>
+    <t>remainder</t>
+  </si>
+  <si>
+    <t>剩余部分</t>
+  </si>
+  <si>
+    <t>representation learning</t>
+  </si>
+  <si>
+    <t>表示学习</t>
+  </si>
+  <si>
+    <t>residual</t>
+  </si>
+  <si>
+    <t>残留的</t>
+  </si>
+  <si>
+    <t>resolutions</t>
+  </si>
+  <si>
+    <t>分辨率</t>
+  </si>
+  <si>
+    <t>retrieval</t>
+  </si>
+  <si>
+    <t>检索</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>回顾</t>
+  </si>
+  <si>
+    <t>robust</t>
+  </si>
+  <si>
+    <t>adj.强壮的,即鲁棒。/rou ba si te/</t>
+  </si>
+  <si>
+    <t>robustness</t>
+  </si>
+  <si>
+    <t>鲁棒性</t>
+  </si>
+  <si>
+    <t>scalable</t>
+  </si>
+  <si>
+    <t>可扩展的</t>
+  </si>
+  <si>
+    <t>scale</t>
+  </si>
+  <si>
+    <t>v.缩小或放大,攀登 n.规模,范围</t>
+  </si>
+  <si>
+    <t>scaling laws</t>
+  </si>
+  <si>
+    <t>缩放规律</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>范围</t>
+  </si>
+  <si>
+    <t>semantic insights</t>
+  </si>
+  <si>
+    <t>语义信息</t>
+  </si>
+  <si>
+    <t>semantic interaction</t>
+  </si>
+  <si>
+    <t>语义相互 semanteike</t>
+  </si>
+  <si>
+    <t>sequence</t>
+  </si>
+  <si>
+    <t>序列/数列</t>
+  </si>
+  <si>
+    <t>sequentially</t>
+  </si>
+  <si>
+    <t>继续地</t>
+  </si>
+  <si>
+    <t>sequently</t>
+  </si>
+  <si>
+    <t>依次</t>
+  </si>
+  <si>
+    <t>serve as</t>
+  </si>
+  <si>
+    <t>充当</t>
+  </si>
+  <si>
+    <t>sophisicated</t>
+  </si>
+  <si>
+    <t>复杂的</t>
+  </si>
+  <si>
+    <t>span</t>
+  </si>
+  <si>
+    <t>覆盖</t>
+  </si>
+  <si>
+    <t>sparse</t>
+  </si>
+  <si>
+    <t>稀少的</t>
+  </si>
+  <si>
+    <t>Sparse solutions</t>
+  </si>
+  <si>
+    <t>稀疏解</t>
+  </si>
+  <si>
+    <t>sparsity</t>
+  </si>
+  <si>
+    <t>n.稀疏,缺少 siba se tei</t>
+  </si>
+  <si>
+    <t>specific</t>
+  </si>
+  <si>
+    <t>特定的,专属/具体的(描述数值)/分别的</t>
+  </si>
+  <si>
+    <t>specific in conversation</t>
+  </si>
+  <si>
+    <t>对话中特有的</t>
+  </si>
+  <si>
+    <t>specified to modality</t>
+  </si>
+  <si>
+    <t>特定于模态</t>
+  </si>
+  <si>
+    <t>spectrum</t>
+  </si>
+  <si>
+    <t>谱系</t>
+  </si>
+  <si>
+    <t>Stacked</t>
+  </si>
+  <si>
+    <t>堆叠的</t>
+  </si>
+  <si>
+    <t>stark</t>
+  </si>
+  <si>
+    <t>鲜明地</t>
+  </si>
+  <si>
+    <t>state of the art</t>
+  </si>
+  <si>
+    <t>最先进的</t>
+  </si>
+  <si>
+    <t>submodule</t>
+  </si>
+  <si>
+    <t>子模块</t>
+  </si>
+  <si>
+    <t>suboptimal</t>
+  </si>
+  <si>
+    <t>次最优的</t>
+  </si>
+  <si>
+    <t>subsection</t>
+  </si>
+  <si>
+    <t>分段,分片</t>
+  </si>
+  <si>
+    <t>subsequently</t>
+  </si>
+  <si>
+    <t>随后</t>
+  </si>
+  <si>
+    <t>subset</t>
+  </si>
+  <si>
+    <t>子集</t>
+  </si>
+  <si>
+    <t>substantial</t>
+  </si>
+  <si>
+    <t>大量的,巨大的</t>
+  </si>
+  <si>
+    <t>supervision</t>
+  </si>
+  <si>
+    <t>监督</t>
+  </si>
+  <si>
+    <t>task-oriented</t>
+  </si>
+  <si>
+    <t>任务导向</t>
   </si>
   <si>
     <t>template</t>
@@ -71,88 +1470,124 @@
     <t>模板</t>
   </si>
   <si>
-    <t>manual</t>
-  </si>
-  <si>
-    <t>人工,手工</t>
-  </si>
-  <si>
-    <t>Discrete</t>
-  </si>
-  <si>
-    <t>离散</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>连续</t>
-  </si>
-  <si>
-    <t>intuitive</t>
-  </si>
-  <si>
-    <t>直觉的,直观的</t>
-  </si>
-  <si>
-    <t>coherence</t>
-  </si>
-  <si>
-    <t>连贯性,条理性</t>
-  </si>
-  <si>
-    <t>homepage</t>
-  </si>
-  <si>
-    <t>首页</t>
-  </si>
-  <si>
-    <t>affect or feelings</t>
-  </si>
-  <si>
-    <t>情感或感受</t>
-  </si>
-  <si>
-    <t>intentions</t>
-  </si>
-  <si>
-    <t>意图</t>
-  </si>
-  <si>
-    <t>Concretely</t>
-  </si>
-  <si>
-    <t>具体的</t>
-  </si>
-  <si>
-    <t>dialog</t>
-  </si>
-  <si>
-    <t>对话</t>
-  </si>
-  <si>
-    <t>empathetic</t>
-  </si>
-  <si>
-    <t>同感</t>
-  </si>
-  <si>
-    <t>generate</t>
-  </si>
-  <si>
-    <t>生成</t>
-  </si>
-  <si>
-    <t>generation</t>
-  </si>
-  <si>
-    <t>生成,后代</t>
-  </si>
-  <si>
-    <t>detect</t>
-  </si>
-  <si>
-    <t>查明,探查</t>
+    <t>text components</t>
+  </si>
+  <si>
+    <t>文本组件</t>
+  </si>
+  <si>
+    <t>thereby</t>
+  </si>
+  <si>
+    <t>从而</t>
+  </si>
+  <si>
+    <t>this advancement</t>
+  </si>
+  <si>
+    <t>这一进展</t>
+  </si>
+  <si>
+    <t>Tokens</t>
+  </si>
+  <si>
+    <t>令牌,代币</t>
+  </si>
+  <si>
+    <t>tone</t>
+  </si>
+  <si>
+    <t>语气 说话时的整体情感色彩比如愤怒</t>
+  </si>
+  <si>
+    <t>towards</t>
+  </si>
+  <si>
+    <t>迈向</t>
+  </si>
+  <si>
+    <t>trade-off</t>
+  </si>
+  <si>
+    <t>权衡</t>
+  </si>
+  <si>
+    <t>transformation</t>
+  </si>
+  <si>
+    <t>变化</t>
+  </si>
+  <si>
+    <t>transition</t>
+  </si>
+  <si>
+    <t>转变</t>
+  </si>
+  <si>
+    <t>tunes</t>
+  </si>
+  <si>
+    <t>微调</t>
+  </si>
+  <si>
+    <t>two-fold</t>
+  </si>
+  <si>
+    <t>双重的</t>
+  </si>
+  <si>
+    <t>uncover</t>
+  </si>
+  <si>
+    <t>揭露,发现</t>
+  </si>
+  <si>
+    <t>underlying</t>
+  </si>
+  <si>
+    <t>潜在的</t>
+  </si>
+  <si>
+    <t>undirect edges</t>
+  </si>
+  <si>
+    <t>无向边</t>
+  </si>
+  <si>
+    <t>unfilled slots</t>
+  </si>
+  <si>
+    <t>未填充槽位</t>
+  </si>
+  <si>
+    <t>unified</t>
+  </si>
+  <si>
+    <t>统一</t>
+  </si>
+  <si>
+    <t>unimodal</t>
+  </si>
+  <si>
+    <t>单模态</t>
+  </si>
+  <si>
+    <t>univariate</t>
+  </si>
+  <si>
+    <t>单变量</t>
+  </si>
+  <si>
+    <t>utterance aoterunsi</t>
+  </si>
+  <si>
+    <t>话语,言论</t>
+  </si>
+  <si>
+    <t>visual</t>
+  </si>
+  <si>
+    <t>视觉的</t>
   </si>
   <si>
     <t>while</t>
@@ -167,1117 +1602,16 @@
     <t>当训练时</t>
   </si>
   <si>
-    <t>illustration</t>
-  </si>
-  <si>
-    <t>示意图,图解</t>
-  </si>
-  <si>
-    <t>Casual</t>
-  </si>
-  <si>
-    <t>因果</t>
-  </si>
-  <si>
-    <t>Casuality</t>
-  </si>
-  <si>
-    <t>因果关系</t>
-  </si>
-  <si>
-    <t>inference</t>
-  </si>
-  <si>
-    <t>推理</t>
-  </si>
-  <si>
-    <t>specified to modality</t>
-  </si>
-  <si>
-    <t>特定于模态</t>
-  </si>
-  <si>
-    <t>task-oriented</t>
-  </si>
-  <si>
-    <t>任务导向</t>
-  </si>
-  <si>
-    <t>implements</t>
-  </si>
-  <si>
-    <t>实现</t>
-  </si>
-  <si>
-    <t>state of the art</t>
-  </si>
-  <si>
-    <t>最先进的</t>
-  </si>
-  <si>
-    <t>consistent</t>
-  </si>
-  <si>
-    <t>一致的</t>
-  </si>
-  <si>
-    <t>interdependent</t>
-  </si>
-  <si>
-    <t>相互依赖的</t>
-  </si>
-  <si>
-    <t>mutually influential</t>
-  </si>
-  <si>
-    <t>相互影响</t>
-  </si>
-  <si>
-    <t>serve as</t>
-  </si>
-  <si>
-    <t>充当</t>
-  </si>
-  <si>
-    <t>Complementary knowledge</t>
-  </si>
-  <si>
-    <t>互补知识</t>
-  </si>
-  <si>
-    <t>underlying</t>
-  </si>
-  <si>
-    <t>潜在的</t>
-  </si>
-  <si>
-    <t>emotion and sentiment</t>
-  </si>
-  <si>
-    <t>情感和情绪</t>
-  </si>
-  <si>
-    <t>casual nature</t>
-  </si>
-  <si>
-    <t>因果本质</t>
-  </si>
-  <si>
-    <t>thereby</t>
-  </si>
-  <si>
-    <t>从而</t>
-  </si>
-  <si>
-    <t>further demostrating</t>
-  </si>
-  <si>
-    <t>进一步证明</t>
-  </si>
-  <si>
-    <t>paradigm</t>
-  </si>
-  <si>
-    <t>范式</t>
-  </si>
-  <si>
-    <t>overlook</t>
-  </si>
-  <si>
-    <t>忽略</t>
-  </si>
-  <si>
-    <t>adaptive</t>
-  </si>
-  <si>
-    <t>适应的,有能力</t>
-  </si>
-  <si>
-    <t>adaptive hybrid</t>
-  </si>
-  <si>
-    <t>自适应融合</t>
-  </si>
-  <si>
-    <t>towards</t>
-  </si>
-  <si>
-    <t>迈向</t>
-  </si>
-  <si>
-    <t>unified</t>
-  </si>
-  <si>
-    <t>统一</t>
-  </si>
-  <si>
-    <t>cause</t>
-  </si>
-  <si>
-    <t>n.原因,理由</t>
-  </si>
-  <si>
-    <t>recognition</t>
-  </si>
-  <si>
-    <t>n.识别,承认</t>
-  </si>
-  <si>
-    <t>reading comprehension</t>
-  </si>
-  <si>
-    <t>阅读理解</t>
-  </si>
-  <si>
-    <t>framework</t>
-  </si>
-  <si>
-    <t>框架</t>
-  </si>
-  <si>
-    <t>evolve into</t>
-  </si>
-  <si>
-    <t>逐渐演变成</t>
-  </si>
-  <si>
-    <t>Methodology</t>
-  </si>
-  <si>
-    <t>方法论</t>
-  </si>
-  <si>
-    <t>Auxiliary</t>
-  </si>
-  <si>
-    <t>辅助</t>
-  </si>
-  <si>
-    <t>prompts</t>
-  </si>
-  <si>
-    <t>提示词</t>
-  </si>
-  <si>
-    <t>Tokens</t>
-  </si>
-  <si>
-    <t>令牌,代币</t>
-  </si>
-  <si>
-    <t>Mask</t>
-  </si>
-  <si>
-    <t>掩码</t>
-  </si>
-  <si>
-    <t>denote...respectively</t>
-  </si>
-  <si>
-    <t>分别表示</t>
-  </si>
-  <si>
-    <t>utterance aoterunsi</t>
-  </si>
-  <si>
-    <t>话语,言论</t>
-  </si>
-  <si>
-    <t>multi-turn</t>
-  </si>
-  <si>
-    <t>多轮对话</t>
-  </si>
-  <si>
-    <t>emotion specific representation</t>
-  </si>
-  <si>
-    <t>情感特定表征,某个句子整体情感向量</t>
-  </si>
-  <si>
-    <t>Language model</t>
-  </si>
-  <si>
-    <t>语言模型</t>
-  </si>
-  <si>
-    <t>acoustic</t>
-  </si>
-  <si>
-    <t>声音的</t>
-  </si>
-  <si>
-    <t>visual</t>
-  </si>
-  <si>
-    <t>视觉的</t>
-  </si>
-  <si>
-    <t>unfilled slots</t>
-  </si>
-  <si>
-    <t>未填充槽位</t>
-  </si>
-  <si>
-    <t>leverage</t>
-  </si>
-  <si>
-    <t>充分利用</t>
-  </si>
-  <si>
-    <t>model effect</t>
-  </si>
-  <si>
-    <t>模型影响</t>
-  </si>
-  <si>
-    <t>probe</t>
-  </si>
-  <si>
-    <t>探查</t>
-  </si>
-  <si>
-    <t>specific</t>
-  </si>
-  <si>
-    <t>特定的,专属/具体的(描述数值)/分别的</t>
-  </si>
-  <si>
-    <t>modality-specific featuers</t>
-  </si>
-  <si>
-    <t>模态特定特征</t>
-  </si>
-  <si>
-    <t>inter-modality</t>
-  </si>
-  <si>
-    <t>模型间</t>
-  </si>
-  <si>
-    <t>enable</t>
-  </si>
-  <si>
-    <t>使实现</t>
-  </si>
-  <si>
-    <t>semantic interaction</t>
-  </si>
-  <si>
-    <t>语义相互 semanteike</t>
-  </si>
-  <si>
-    <t>representation learning</t>
-  </si>
-  <si>
-    <t>表示学习</t>
-  </si>
-  <si>
-    <t>indicate</t>
-  </si>
-  <si>
-    <t>显示/表明，指明/验证</t>
-  </si>
-  <si>
-    <t>Given</t>
-  </si>
-  <si>
-    <t>给定,对于</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>类别</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>序列/数列</t>
-  </si>
-  <si>
-    <t>processed</t>
-  </si>
-  <si>
-    <t>处理</t>
-  </si>
-  <si>
-    <t>raw acoustic input</t>
-  </si>
-  <si>
-    <t>原始音频输入</t>
-  </si>
-  <si>
-    <t>numerical sequential vectors</t>
-  </si>
-  <si>
-    <t>数值连续向量</t>
-  </si>
-  <si>
-    <t>Explicit</t>
-  </si>
-  <si>
-    <t>显式</t>
-  </si>
-  <si>
-    <t>implicit</t>
-  </si>
-  <si>
-    <t>隐式</t>
-  </si>
-  <si>
-    <t>alignment</t>
-  </si>
-  <si>
-    <t>对齐</t>
-  </si>
-  <si>
-    <t>backbone</t>
-  </si>
-  <si>
-    <t>脊梁,基础</t>
-  </si>
-  <si>
-    <t>Stacked</t>
-  </si>
-  <si>
-    <t>堆叠的</t>
-  </si>
-  <si>
-    <t>Layer</t>
-  </si>
-  <si>
-    <t>层</t>
-  </si>
-  <si>
-    <t>Normalization</t>
-  </si>
-  <si>
-    <t>规划化</t>
-  </si>
-  <si>
-    <t>supervision</t>
-  </si>
-  <si>
-    <t>监督</t>
-  </si>
-  <si>
-    <t>real groud</t>
-  </si>
-  <si>
-    <t>真实答案下</t>
-  </si>
-  <si>
-    <t>fusion</t>
-  </si>
-  <si>
-    <t>融合</t>
-  </si>
-  <si>
-    <t>concatenation</t>
-  </si>
-  <si>
-    <t>拼接</t>
-  </si>
-  <si>
-    <t>modal fusion representations</t>
-  </si>
-  <si>
-    <t>模型融合表征</t>
-  </si>
-  <si>
-    <t>hierarchical</t>
-  </si>
-  <si>
-    <t>分层的 Hier神圣的,arch统治者</t>
-  </si>
-  <si>
-    <t>learned representations</t>
-  </si>
-  <si>
-    <t>习得表征</t>
-  </si>
-  <si>
-    <t>incorporate</t>
-  </si>
-  <si>
-    <t>包含,使并入</t>
-  </si>
-  <si>
-    <t>aggregation</t>
-  </si>
-  <si>
-    <t>聚集,集合</t>
-  </si>
-  <si>
-    <t>context</t>
-  </si>
-  <si>
-    <t>上下文,背景</t>
-  </si>
-  <si>
-    <t>content</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>intra</t>
-  </si>
-  <si>
-    <t>层内</t>
-  </si>
-  <si>
-    <t>inter</t>
-  </si>
-  <si>
-    <t>跨层</t>
-  </si>
-  <si>
-    <t>undirect edges</t>
-  </si>
-  <si>
-    <t>无向边</t>
-  </si>
-  <si>
-    <t>adjacent ao G sen te</t>
-  </si>
-  <si>
-    <t>邻近的</t>
-  </si>
-  <si>
-    <t>Grouding</t>
-  </si>
-  <si>
-    <t>关联/接地/对齐</t>
-  </si>
-  <si>
-    <t>benchmark datasets</t>
-  </si>
-  <si>
-    <t>基准数据集</t>
-  </si>
-  <si>
-    <t>multi-party</t>
-  </si>
-  <si>
-    <t>多方</t>
-  </si>
-  <si>
-    <t>annotated labels</t>
-  </si>
-  <si>
-    <t>带注释的标签</t>
-  </si>
-  <si>
-    <t>operation</t>
-  </si>
-  <si>
-    <t>操作,设计</t>
-  </si>
-  <si>
-    <t>decay</t>
-  </si>
-  <si>
-    <t>v.衰减</t>
-  </si>
-  <si>
-    <t>illustrate</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>modelling</t>
-  </si>
-  <si>
-    <t>建模</t>
-  </si>
-  <si>
-    <t>jointly training</t>
-  </si>
-  <si>
-    <t>联合训练</t>
-  </si>
-  <si>
-    <t>ablation study</t>
-  </si>
-  <si>
-    <t>消融实验</t>
-  </si>
-  <si>
-    <t>extensive</t>
-  </si>
-  <si>
-    <t>全面的,大量的</t>
-  </si>
-  <si>
-    <t>disorder</t>
-  </si>
-  <si>
-    <t>扰乱</t>
-  </si>
-  <si>
-    <t>disrupt</t>
-  </si>
-  <si>
-    <t>中断,扰乱</t>
-  </si>
-  <si>
-    <t>reformulate</t>
-  </si>
-  <si>
-    <t>重新表述</t>
-  </si>
-  <si>
-    <t>tunes</t>
-  </si>
-  <si>
-    <t>微调</t>
-  </si>
-  <si>
-    <t>metrics</t>
-  </si>
-  <si>
-    <t>指标</t>
-  </si>
-  <si>
-    <t>further</t>
-  </si>
-  <si>
-    <t>更远的,进一步</t>
-  </si>
-  <si>
-    <t>unimodal</t>
-  </si>
-  <si>
-    <t>单模态</t>
-  </si>
-  <si>
-    <t>consistency</t>
-  </si>
-  <si>
-    <t>一致性</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>ethics statement</t>
-  </si>
-  <si>
-    <t>道德说明</t>
-  </si>
-  <si>
-    <t>proposed method</t>
-  </si>
-  <si>
-    <t>所提方法</t>
-  </si>
-  <si>
-    <t>multi-class</t>
-  </si>
-  <si>
-    <t>多类别</t>
-  </si>
-  <si>
-    <t>appealing</t>
-  </si>
-  <si>
-    <t>影响力</t>
-  </si>
-  <si>
-    <t>Acknowledgement</t>
-  </si>
-  <si>
-    <t>致谢</t>
-  </si>
-  <si>
-    <t>empathetic Companion</t>
-  </si>
-  <si>
-    <t>共情陪伴</t>
-  </si>
-  <si>
-    <t>fusion mechanism</t>
-  </si>
-  <si>
-    <t>融合机制</t>
-  </si>
-  <si>
-    <t>hinder</t>
-  </si>
-  <si>
-    <t>阻碍,制约</t>
-  </si>
-  <si>
-    <t>account for</t>
-  </si>
-  <si>
-    <t>解决,处理,考虑到</t>
-  </si>
-  <si>
-    <t>inherent</t>
-  </si>
-  <si>
-    <t>天然的,固有的</t>
-  </si>
-  <si>
-    <t>specific in conversation</t>
-  </si>
-  <si>
-    <t>对话中特有的</t>
-  </si>
-  <si>
-    <t>local cause query</t>
-  </si>
-  <si>
-    <t>局部原因查询</t>
-  </si>
-  <si>
-    <t>subsequently</t>
-  </si>
-  <si>
-    <t>随后</t>
-  </si>
-  <si>
-    <t>in the literature</t>
-  </si>
-  <si>
-    <t>在文献中</t>
-  </si>
-  <si>
-    <t>often embedded</t>
-  </si>
-  <si>
-    <t>总是蕴含着</t>
-  </si>
-  <si>
-    <t>nuanced</t>
-  </si>
-  <si>
-    <t>微妙地</t>
-  </si>
-  <si>
-    <t>uncover</t>
-  </si>
-  <si>
-    <t>揭露,发现</t>
-  </si>
-  <si>
-    <t>semantic insights</t>
-  </si>
-  <si>
-    <t>语义信息</t>
-  </si>
-  <si>
-    <t>in essence</t>
-  </si>
-  <si>
-    <t>从本质上</t>
-  </si>
-  <si>
-    <t>encompassing</t>
-  </si>
-  <si>
-    <t>包含,涵盖</t>
-  </si>
-  <si>
-    <t>conversational dialogue</t>
-  </si>
-  <si>
-    <t>口语对话/对话</t>
-  </si>
-  <si>
-    <t>text components</t>
-  </si>
-  <si>
-    <t>文本组件</t>
-  </si>
-  <si>
-    <t>linguistic cues</t>
-  </si>
-  <si>
-    <t>语言线索</t>
-  </si>
-  <si>
-    <t>convey</t>
-  </si>
-  <si>
-    <t>传达</t>
-  </si>
-  <si>
-    <t>encapsulate</t>
-  </si>
-  <si>
-    <t>概述、封装</t>
-  </si>
-  <si>
-    <t>tone</t>
-  </si>
-  <si>
-    <t>语气 说话时的整体情感色彩比如愤怒</t>
-  </si>
-  <si>
-    <t>intonation</t>
-  </si>
-  <si>
-    <t>语调 句子整体的音调起伏模式 陈述句下降</t>
-  </si>
-  <si>
-    <t>pitch</t>
-  </si>
-  <si>
-    <t>音高 声音的频率高低,高低音</t>
-  </si>
-  <si>
-    <t>holistic</t>
-  </si>
-  <si>
-    <t>整体的,全面的</t>
-  </si>
-  <si>
-    <t>complementary insights</t>
-  </si>
-  <si>
-    <t>互补洞察</t>
-  </si>
-  <si>
-    <t>spectrum</t>
-  </si>
-  <si>
-    <t>谱系</t>
-  </si>
-  <si>
-    <t>comprehensive</t>
-  </si>
-  <si>
-    <t>全面的</t>
-  </si>
-  <si>
-    <t>this advancement</t>
-  </si>
-  <si>
-    <t>这一进展</t>
-  </si>
-  <si>
-    <t>innovative</t>
-  </si>
-  <si>
-    <t>创新</t>
-  </si>
-  <si>
-    <t>examining</t>
-  </si>
-  <si>
-    <t>审视,检查</t>
-  </si>
-  <si>
-    <t>identify</t>
-  </si>
-  <si>
-    <t>识别出</t>
-  </si>
-  <si>
-    <t>constitute</t>
-  </si>
-  <si>
-    <t>组成,构成</t>
-  </si>
-  <si>
-    <t>imperative</t>
-  </si>
-  <si>
-    <t>极其重要的</t>
-  </si>
-  <si>
-    <t>sophisicated</t>
-  </si>
-  <si>
-    <t>复杂的</t>
-  </si>
-  <si>
-    <t>suboptimal</t>
-  </si>
-  <si>
-    <t>次最优的</t>
-  </si>
-  <si>
-    <t>facilitating</t>
-  </si>
-  <si>
-    <t>使更容易,促进</t>
-  </si>
-  <si>
-    <t>consequently</t>
-  </si>
-  <si>
-    <t>因此,结果</t>
-  </si>
-  <si>
-    <t>aforementioned</t>
-  </si>
-  <si>
-    <t>上述的</t>
-  </si>
-  <si>
-    <t>correlated</t>
-  </si>
-  <si>
-    <t>被关联</t>
-  </si>
-  <si>
-    <t>global</t>
-  </si>
-  <si>
-    <t>全局</t>
-  </si>
-  <si>
-    <t>scope</t>
-  </si>
-  <si>
-    <t>范围</t>
-  </si>
-  <si>
-    <t>in summary</t>
-  </si>
-  <si>
-    <t>总之,概况起来</t>
-  </si>
-  <si>
-    <t>attention module</t>
-  </si>
-  <si>
-    <t>注意力模块</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>约束</t>
-  </si>
-  <si>
-    <t>conduct</t>
-  </si>
-  <si>
-    <t>进行</t>
-  </si>
-  <si>
-    <t>remainder</t>
-  </si>
-  <si>
-    <t>剩余部分</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>回顾</t>
-  </si>
-  <si>
-    <t>elaboration</t>
-  </si>
-  <si>
-    <t>详细阐述</t>
-  </si>
-  <si>
-    <t>hyper-parameter</t>
-  </si>
-  <si>
-    <t>超参数</t>
-  </si>
-  <si>
-    <t>case study</t>
-  </si>
-  <si>
-    <t>案例研究</t>
-  </si>
-  <si>
-    <t>conclude</t>
-  </si>
-  <si>
-    <t>推断,总结</t>
-  </si>
-  <si>
-    <t>outline</t>
-  </si>
-  <si>
-    <t>v.概述 n.轮廓</t>
-  </si>
-  <si>
-    <t>critical</t>
-  </si>
-  <si>
-    <t>关键</t>
-  </si>
-  <si>
-    <t>integrate</t>
-  </si>
-  <si>
-    <t>robustness</t>
-  </si>
-  <si>
-    <t>鲁棒性</t>
-  </si>
-  <si>
-    <t>context construction</t>
-  </si>
-  <si>
-    <t>上下文结构</t>
-  </si>
-  <si>
-    <t>employ</t>
-  </si>
-  <si>
-    <t>采用</t>
-  </si>
-  <si>
-    <t>coined</t>
-  </si>
-  <si>
-    <t>创造</t>
-  </si>
-  <si>
-    <t>pre-specifying</t>
-  </si>
-  <si>
-    <t>预格式化,预指定</t>
-  </si>
-  <si>
-    <t>transition</t>
-  </si>
-  <si>
-    <t>转变</t>
-  </si>
-  <si>
-    <t>in light of</t>
-  </si>
-  <si>
-    <t>基于某种情况,鉴于</t>
-  </si>
-  <si>
-    <t>extant</t>
-  </si>
-  <si>
-    <t>现存的</t>
-  </si>
-  <si>
-    <t>note that</t>
-  </si>
-  <si>
-    <t>注意</t>
-  </si>
-  <si>
-    <t>in practice</t>
-  </si>
-  <si>
-    <t>在实践中</t>
-  </si>
-  <si>
-    <t>a given</t>
-  </si>
-  <si>
-    <t>给定</t>
-  </si>
-  <si>
-    <t>sequentially</t>
-  </si>
-  <si>
-    <t>继续地</t>
-  </si>
-  <si>
-    <t>subsection</t>
-  </si>
-  <si>
-    <t>分段,分片</t>
-  </si>
-  <si>
-    <t>corpus</t>
-  </si>
-  <si>
-    <t>语料库,全集</t>
-  </si>
-  <si>
-    <t>prefix</t>
-  </si>
-  <si>
-    <t>前缀</t>
-  </si>
-  <si>
-    <t>submodule</t>
-  </si>
-  <si>
-    <t>子模块</t>
-  </si>
-  <si>
-    <t>For the sake of</t>
-  </si>
-  <si>
-    <t>出于...目的</t>
-  </si>
-  <si>
-    <t>brevity</t>
-  </si>
-  <si>
-    <t>简介,短暂</t>
-  </si>
-  <si>
-    <t>residual</t>
-  </si>
-  <si>
-    <t>残留的</t>
-  </si>
-  <si>
-    <t>generalization</t>
-  </si>
-  <si>
-    <t>概括,泛化</t>
-  </si>
-  <si>
-    <t>Feed forward Network</t>
-  </si>
-  <si>
-    <t>前倾网络</t>
-  </si>
-  <si>
-    <t>transformation</t>
-  </si>
-  <si>
-    <t>变化</t>
-  </si>
-  <si>
-    <t>sequently</t>
-  </si>
-  <si>
-    <t>依次</t>
-  </si>
-  <si>
-    <t>rectify</t>
-  </si>
-  <si>
-    <t>纠正</t>
-  </si>
-  <si>
-    <t>exploit</t>
-  </si>
-  <si>
-    <t>利用</t>
-  </si>
-  <si>
-    <t>Discrepancy</t>
-  </si>
-  <si>
-    <t>差异</t>
-  </si>
-  <si>
-    <t>bridging discrepancy</t>
-  </si>
-  <si>
-    <t>弥合差距</t>
+    <t>zero shot</t>
+  </si>
+  <si>
+    <t>零样本</t>
+  </si>
+  <si>
+    <t>delve into</t>
+  </si>
+  <si>
+    <t>v.深入探究</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1624,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1302,6 +1636,18 @@
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.95"/>
+      <color rgb="FF000000"/>
+      <name val="NimbusRomNo9L-Regu"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1775,137 +2121,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1913,6 +2259,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2447,7 +2799,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:C209"/>
+  <dimension ref="B1:C260"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20.6388888888889" customWidth="1"/>
@@ -2968,7 +3320,7 @@
       </c>
     </row>
     <row r="65" spans="2:3">
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>128</v>
       </c>
       <c r="C65" t="s">
@@ -2976,7 +3328,7 @@
       </c>
     </row>
     <row r="66" spans="2:3">
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>130</v>
       </c>
       <c r="C66" t="s">
@@ -3108,1026 +3460,1437 @@
         <v>162</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="B83" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83" t="s">
         <v>164</v>
-      </c>
-      <c r="C83" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="84" spans="2:3">
       <c r="B84" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" t="s">
         <v>166</v>
-      </c>
-      <c r="C84" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="85" spans="2:3">
       <c r="B85" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" t="s">
         <v>168</v>
-      </c>
-      <c r="C85" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="B86" t="s">
+        <v>169</v>
+      </c>
+      <c r="C86" t="s">
         <v>170</v>
-      </c>
-      <c r="C86" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="87" spans="2:3">
       <c r="B87" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" t="s">
         <v>172</v>
       </c>
-      <c r="C87" t="s">
+    </row>
+    <row r="88" spans="2:3">
+      <c r="B88" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="88" spans="2:3">
-      <c r="B88" t="s">
+      <c r="C88" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C88" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="B89" t="s">
+        <v>175</v>
+      </c>
+      <c r="C89" t="s">
         <v>176</v>
-      </c>
-      <c r="C89" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="B90" t="s">
+        <v>177</v>
+      </c>
+      <c r="C90" t="s">
         <v>178</v>
-      </c>
-      <c r="C90" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" t="s">
+        <v>179</v>
+      </c>
+      <c r="C91" t="s">
         <v>180</v>
-      </c>
-      <c r="C91" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="B92" t="s">
+        <v>181</v>
+      </c>
+      <c r="C92" t="s">
         <v>182</v>
-      </c>
-      <c r="C92" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="B93" t="s">
+        <v>183</v>
+      </c>
+      <c r="C93" t="s">
         <v>184</v>
-      </c>
-      <c r="C93" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="B94" t="s">
+        <v>185</v>
+      </c>
+      <c r="C94" t="s">
         <v>186</v>
-      </c>
-      <c r="C94" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="B95" t="s">
+        <v>187</v>
+      </c>
+      <c r="C95" t="s">
         <v>188</v>
-      </c>
-      <c r="C95" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="96" spans="2:3">
       <c r="B96" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" t="s">
         <v>190</v>
-      </c>
-      <c r="C96" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="97" spans="2:3">
       <c r="B97" t="s">
+        <v>191</v>
+      </c>
+      <c r="C97" t="s">
         <v>192</v>
-      </c>
-      <c r="C97" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="B98" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98" t="s">
         <v>194</v>
-      </c>
-      <c r="C98" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="B99" t="s">
+        <v>195</v>
+      </c>
+      <c r="C99" t="s">
         <v>196</v>
-      </c>
-      <c r="C99" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="B100" t="s">
+        <v>197</v>
+      </c>
+      <c r="C100" t="s">
         <v>198</v>
-      </c>
-      <c r="C100" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="B101" t="s">
+        <v>199</v>
+      </c>
+      <c r="C101" t="s">
         <v>200</v>
-      </c>
-      <c r="C101" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="102" spans="2:3">
       <c r="B102" t="s">
+        <v>201</v>
+      </c>
+      <c r="C102" t="s">
         <v>202</v>
-      </c>
-      <c r="C102" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
+        <v>203</v>
+      </c>
+      <c r="C103" t="s">
         <v>204</v>
-      </c>
-      <c r="C103" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="B104" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" t="s">
         <v>206</v>
-      </c>
-      <c r="C104" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="B105" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105" t="s">
         <v>208</v>
-      </c>
-      <c r="C105" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" t="s">
         <v>210</v>
-      </c>
-      <c r="C106" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="B107" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" t="s">
         <v>212</v>
-      </c>
-      <c r="C107" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="B108" t="s">
+        <v>213</v>
+      </c>
+      <c r="C108" t="s">
         <v>214</v>
-      </c>
-      <c r="C108" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="B109" t="s">
+        <v>215</v>
+      </c>
+      <c r="C109" t="s">
         <v>216</v>
-      </c>
-      <c r="C109" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="B110" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" t="s">
         <v>218</v>
-      </c>
-      <c r="C110" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="B111" t="s">
+        <v>219</v>
+      </c>
+      <c r="C111" t="s">
         <v>220</v>
-      </c>
-      <c r="C111" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="B112" t="s">
+        <v>221</v>
+      </c>
+      <c r="C112" t="s">
         <v>222</v>
-      </c>
-      <c r="C112" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="B113" t="s">
+        <v>223</v>
+      </c>
+      <c r="C113" t="s">
         <v>224</v>
-      </c>
-      <c r="C113" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="B114" t="s">
+        <v>225</v>
+      </c>
+      <c r="C114" t="s">
         <v>226</v>
-      </c>
-      <c r="C114" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="115" spans="2:3">
       <c r="B115" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" t="s">
         <v>228</v>
-      </c>
-      <c r="C115" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="116" spans="2:3">
       <c r="B116" t="s">
+        <v>229</v>
+      </c>
+      <c r="C116" t="s">
         <v>230</v>
-      </c>
-      <c r="C116" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="117" spans="2:3">
       <c r="B117" t="s">
+        <v>231</v>
+      </c>
+      <c r="C117" t="s">
         <v>232</v>
-      </c>
-      <c r="C117" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="118" spans="2:3">
       <c r="B118" t="s">
+        <v>233</v>
+      </c>
+      <c r="C118" t="s">
         <v>234</v>
-      </c>
-      <c r="C118" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="119" spans="2:3">
       <c r="B119" t="s">
+        <v>235</v>
+      </c>
+      <c r="C119" t="s">
         <v>236</v>
-      </c>
-      <c r="C119" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="120" spans="2:3">
       <c r="B120" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" t="s">
         <v>238</v>
-      </c>
-      <c r="C120" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="121" spans="2:3">
       <c r="B121" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" t="s">
         <v>240</v>
-      </c>
-      <c r="C121" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="122" spans="2:3">
       <c r="B122" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" t="s">
         <v>242</v>
-      </c>
-      <c r="C122" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="123" spans="2:3">
       <c r="B123" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" t="s">
         <v>244</v>
-      </c>
-      <c r="C123" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="124" spans="2:3">
       <c r="B124" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" t="s">
         <v>246</v>
-      </c>
-      <c r="C124" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="125" spans="2:3">
       <c r="B125" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" t="s">
         <v>248</v>
-      </c>
-      <c r="C125" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="126" spans="2:3">
       <c r="B126" t="s">
+        <v>249</v>
+      </c>
+      <c r="C126" t="s">
         <v>250</v>
-      </c>
-      <c r="C126" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="127" spans="2:3">
       <c r="B127" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" t="s">
         <v>252</v>
-      </c>
-      <c r="C127" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="128" spans="2:3">
       <c r="B128" t="s">
+        <v>253</v>
+      </c>
+      <c r="C128" t="s">
         <v>254</v>
-      </c>
-      <c r="C128" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="129" spans="2:3">
       <c r="B129" t="s">
+        <v>255</v>
+      </c>
+      <c r="C129" t="s">
         <v>256</v>
-      </c>
-      <c r="C129" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="130" spans="2:3">
       <c r="B130" t="s">
+        <v>257</v>
+      </c>
+      <c r="C130" t="s">
         <v>258</v>
-      </c>
-      <c r="C130" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="131" spans="2:3">
       <c r="B131" t="s">
+        <v>259</v>
+      </c>
+      <c r="C131" t="s">
         <v>260</v>
-      </c>
-      <c r="C131" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="132" spans="2:3">
       <c r="B132" t="s">
+        <v>261</v>
+      </c>
+      <c r="C132" t="s">
         <v>262</v>
-      </c>
-      <c r="C132" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="133" spans="2:3">
       <c r="B133" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C133" t="s">
-        <v>265</v>
+        <v>200</v>
       </c>
     </row>
     <row r="134" spans="2:3">
       <c r="B134" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C134" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="135" spans="2:3">
       <c r="B135" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C135" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="2:3">
       <c r="B136" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C136" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="2:3">
       <c r="B137" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C137" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="138" spans="2:3">
       <c r="B138" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C138" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="139" spans="2:3">
       <c r="B139" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C139" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="140" spans="2:3">
       <c r="B140" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C140" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="2:3">
       <c r="B141" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C141" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="142" spans="2:3">
       <c r="B142" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C142" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="143" spans="2:3">
       <c r="B143" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C143" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="144" spans="2:3">
       <c r="B144" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C144" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="145" spans="2:3">
       <c r="B145" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C145" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="146" spans="2:3">
       <c r="B146" t="s">
+        <v>288</v>
+      </c>
+      <c r="C146" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3">
+      <c r="B147" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>291</v>
-      </c>
-    </row>
-    <row r="147" spans="2:3">
-      <c r="B147" t="s">
-        <v>292</v>
-      </c>
-      <c r="C147" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="148" spans="2:3">
       <c r="B148" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C148" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="149" spans="2:3">
       <c r="B149" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="150" spans="2:3">
       <c r="B150" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C150" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="151" spans="2:3">
       <c r="B151" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C151" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="152" spans="2:3">
       <c r="B152" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C152" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="153" spans="2:3">
       <c r="B153" t="s">
+        <v>302</v>
+      </c>
+      <c r="C153" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="154" spans="2:3">
+      <c r="B154" t="s">
         <v>304</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C154" t="s">
         <v>305</v>
-      </c>
-    </row>
-    <row r="154" ht="16.2" spans="2:3">
-      <c r="B154" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C154" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="155" spans="2:3">
       <c r="B155" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C155" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="156" spans="2:3">
       <c r="B156" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C156" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="157" spans="2:3">
       <c r="B157" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C157" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="158" spans="2:3">
       <c r="B158" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C158" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="159" spans="2:3">
       <c r="B159" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C159" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="160" spans="2:3">
       <c r="B160" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="161" spans="2:3">
       <c r="B161" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C161" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="162" spans="2:3">
       <c r="B162" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C162" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="163" spans="2:3">
       <c r="B163" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="164" spans="2:3">
       <c r="B164" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="B165" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C165" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="166" spans="2:3">
       <c r="B166" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="167" spans="2:3">
       <c r="B167" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C167" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="168" spans="2:3">
       <c r="B168" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C168" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="169" spans="2:3">
       <c r="B169" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C169" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="170" spans="2:3">
       <c r="B170" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C170" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="171" spans="2:3">
       <c r="B171" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C171" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="172" spans="2:3">
       <c r="B172" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C172" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="173" spans="2:3">
       <c r="B173" t="s">
+        <v>342</v>
+      </c>
+      <c r="C173" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="174" spans="2:3">
+      <c r="B174" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C174" s="2" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="174" spans="2:3">
-      <c r="B174" t="s">
-        <v>346</v>
-      </c>
-      <c r="C174" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="175" spans="2:3">
       <c r="B175" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C175" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="176" spans="2:3">
       <c r="B176" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C176" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="177" spans="2:3">
       <c r="B177" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C177" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="2:3">
       <c r="B178" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="179" spans="2:3">
       <c r="B179" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C179" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="180" spans="2:3">
       <c r="B180" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C180" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="181" spans="2:3">
       <c r="B181" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C181" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="182" spans="2:3">
       <c r="B182" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C182" t="s">
-        <v>181</v>
+        <v>361</v>
       </c>
     </row>
     <row r="183" spans="2:3">
       <c r="B183" t="s">
+        <v>362</v>
+      </c>
+      <c r="C183" t="s">
         <v>363</v>
-      </c>
-      <c r="C183" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="184" spans="2:3">
       <c r="B184" t="s">
+        <v>364</v>
+      </c>
+      <c r="C184" t="s">
         <v>365</v>
-      </c>
-      <c r="C184" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="185" spans="2:3">
       <c r="B185" t="s">
+        <v>366</v>
+      </c>
+      <c r="C185" t="s">
         <v>367</v>
-      </c>
-      <c r="C185" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="186" spans="2:3">
       <c r="B186" t="s">
+        <v>368</v>
+      </c>
+      <c r="C186" t="s">
         <v>369</v>
-      </c>
-      <c r="C186" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="187" spans="2:3">
       <c r="B187" t="s">
+        <v>370</v>
+      </c>
+      <c r="C187" t="s">
         <v>371</v>
-      </c>
-      <c r="C187" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="188" spans="2:3">
       <c r="B188" t="s">
+        <v>372</v>
+      </c>
+      <c r="C188" t="s">
         <v>373</v>
-      </c>
-      <c r="C188" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="189" spans="2:3">
       <c r="B189" t="s">
+        <v>374</v>
+      </c>
+      <c r="C189" t="s">
         <v>375</v>
-      </c>
-      <c r="C189" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="190" spans="2:3">
       <c r="B190" t="s">
+        <v>376</v>
+      </c>
+      <c r="C190" t="s">
         <v>377</v>
-      </c>
-      <c r="C190" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="191" spans="2:3">
       <c r="B191" t="s">
+        <v>378</v>
+      </c>
+      <c r="C191" t="s">
         <v>379</v>
-      </c>
-      <c r="C191" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="192" spans="2:3">
       <c r="B192" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" t="s">
         <v>381</v>
-      </c>
-      <c r="C192" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="193" spans="2:3">
       <c r="B193" t="s">
+        <v>382</v>
+      </c>
+      <c r="C193" t="s">
         <v>383</v>
-      </c>
-      <c r="C193" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="194" spans="2:3">
       <c r="B194" t="s">
+        <v>384</v>
+      </c>
+      <c r="C194" t="s">
         <v>385</v>
-      </c>
-      <c r="C194" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:3">
       <c r="B195" t="s">
+        <v>386</v>
+      </c>
+      <c r="C195" t="s">
         <v>387</v>
-      </c>
-      <c r="C195" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="196" spans="2:3">
       <c r="B196" t="s">
+        <v>388</v>
+      </c>
+      <c r="C196" t="s">
         <v>389</v>
-      </c>
-      <c r="C196" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="197" spans="2:3">
       <c r="B197" t="s">
+        <v>390</v>
+      </c>
+      <c r="C197" t="s">
         <v>391</v>
-      </c>
-      <c r="C197" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="198" spans="2:3">
       <c r="B198" t="s">
+        <v>392</v>
+      </c>
+      <c r="C198" t="s">
         <v>393</v>
-      </c>
-      <c r="C198" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="199" spans="2:3">
       <c r="B199" t="s">
+        <v>394</v>
+      </c>
+      <c r="C199" t="s">
         <v>395</v>
-      </c>
-      <c r="C199" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="200" spans="2:3">
       <c r="B200" t="s">
+        <v>396</v>
+      </c>
+      <c r="C200" t="s">
         <v>397</v>
-      </c>
-      <c r="C200" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="201" spans="2:3">
       <c r="B201" t="s">
+        <v>398</v>
+      </c>
+      <c r="C201" t="s">
         <v>399</v>
-      </c>
-      <c r="C201" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="202" spans="2:3">
       <c r="B202" t="s">
+        <v>400</v>
+      </c>
+      <c r="C202" t="s">
         <v>401</v>
       </c>
-      <c r="C202" t="s">
+    </row>
+    <row r="203" spans="2:3">
+      <c r="B203" s="1" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="203" spans="2:3">
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>403</v>
-      </c>
-      <c r="C203" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="204" spans="2:3">
       <c r="B204" t="s">
+        <v>404</v>
+      </c>
+      <c r="C204" t="s">
         <v>405</v>
-      </c>
-      <c r="C204" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="205" spans="2:3">
       <c r="B205" t="s">
+        <v>406</v>
+      </c>
+      <c r="C205" t="s">
         <v>407</v>
-      </c>
-      <c r="C205" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="206" spans="2:3">
       <c r="B206" t="s">
+        <v>408</v>
+      </c>
+      <c r="C206" t="s">
         <v>409</v>
-      </c>
-      <c r="C206" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="207" spans="2:3">
       <c r="B207" t="s">
+        <v>410</v>
+      </c>
+      <c r="C207" t="s">
         <v>411</v>
-      </c>
-      <c r="C207" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="208" spans="2:3">
       <c r="B208" t="s">
+        <v>412</v>
+      </c>
+      <c r="C208" t="s">
         <v>413</v>
-      </c>
-      <c r="C208" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="209" spans="2:3">
       <c r="B209" t="s">
+        <v>414</v>
+      </c>
+      <c r="C209" t="s">
         <v>415</v>
       </c>
-      <c r="C209" t="s">
+    </row>
+    <row r="210" spans="2:3">
+      <c r="B210" t="s">
         <v>416</v>
       </c>
+      <c r="C210" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="211" spans="2:3">
+      <c r="B211" t="s">
+        <v>418</v>
+      </c>
+      <c r="C211" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="212" spans="2:3">
+      <c r="B212" t="s">
+        <v>420</v>
+      </c>
+      <c r="C212" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="213" spans="2:3">
+      <c r="B213" t="s">
+        <v>422</v>
+      </c>
+      <c r="C213" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="214" spans="2:3">
+      <c r="B214" t="s">
+        <v>424</v>
+      </c>
+      <c r="C214" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="215" spans="2:3">
+      <c r="B215" t="s">
+        <v>426</v>
+      </c>
+      <c r="C215" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="216" spans="2:3">
+      <c r="B216" t="s">
+        <v>428</v>
+      </c>
+      <c r="C216" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="217" spans="2:3">
+      <c r="B217" t="s">
+        <v>430</v>
+      </c>
+      <c r="C217" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="218" spans="2:3">
+      <c r="B218" t="s">
+        <v>432</v>
+      </c>
+      <c r="C218" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="219" spans="2:3">
+      <c r="B219" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C219" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="220" spans="2:3">
+      <c r="B220" t="s">
+        <v>436</v>
+      </c>
+      <c r="C220" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="221" spans="2:3">
+      <c r="B221" t="s">
+        <v>438</v>
+      </c>
+      <c r="C221" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="222" spans="2:3">
+      <c r="B222" t="s">
+        <v>440</v>
+      </c>
+      <c r="C222" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="223" spans="2:3">
+      <c r="B223" t="s">
+        <v>442</v>
+      </c>
+      <c r="C223" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="224" ht="16.2" spans="2:3">
+      <c r="B224" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C224" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3">
+      <c r="B225" t="s">
+        <v>446</v>
+      </c>
+      <c r="C225" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3">
+      <c r="B226" t="s">
+        <v>448</v>
+      </c>
+      <c r="C226" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3">
+      <c r="B227" t="s">
+        <v>450</v>
+      </c>
+      <c r="C227" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3">
+      <c r="B228" t="s">
+        <v>452</v>
+      </c>
+      <c r="C228" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3">
+      <c r="B229" t="s">
+        <v>454</v>
+      </c>
+      <c r="C229" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3">
+      <c r="B230" t="s">
+        <v>456</v>
+      </c>
+      <c r="C230" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3">
+      <c r="B231" t="s">
+        <v>458</v>
+      </c>
+      <c r="C231" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3">
+      <c r="B232" t="s">
+        <v>460</v>
+      </c>
+      <c r="C232" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3">
+      <c r="B233" t="s">
+        <v>462</v>
+      </c>
+      <c r="C233" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3">
+      <c r="B234" t="s">
+        <v>464</v>
+      </c>
+      <c r="C234" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3">
+      <c r="B235" t="s">
+        <v>466</v>
+      </c>
+      <c r="C235" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3">
+      <c r="B236" t="s">
+        <v>468</v>
+      </c>
+      <c r="C236" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3">
+      <c r="B237" t="s">
+        <v>470</v>
+      </c>
+      <c r="C237" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3">
+      <c r="B238" t="s">
+        <v>472</v>
+      </c>
+      <c r="C238" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3">
+      <c r="B239" t="s">
+        <v>474</v>
+      </c>
+      <c r="C239" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3">
+      <c r="B240" t="s">
+        <v>476</v>
+      </c>
+      <c r="C240" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3">
+      <c r="B241" t="s">
+        <v>478</v>
+      </c>
+      <c r="C241" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3">
+      <c r="B242" t="s">
+        <v>480</v>
+      </c>
+      <c r="C242" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3">
+      <c r="B243" t="s">
+        <v>482</v>
+      </c>
+      <c r="C243" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3">
+      <c r="B244" t="s">
+        <v>484</v>
+      </c>
+      <c r="C244" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3">
+      <c r="B245" t="s">
+        <v>486</v>
+      </c>
+      <c r="C245" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3">
+      <c r="B246" t="s">
+        <v>488</v>
+      </c>
+      <c r="C246" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3">
+      <c r="B247" t="s">
+        <v>490</v>
+      </c>
+      <c r="C247" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3">
+      <c r="B248" t="s">
+        <v>492</v>
+      </c>
+      <c r="C248" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3">
+      <c r="B249" t="s">
+        <v>494</v>
+      </c>
+      <c r="C249" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3">
+      <c r="B250" t="s">
+        <v>496</v>
+      </c>
+      <c r="C250" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3">
+      <c r="B251" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C251" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3">
+      <c r="B252" t="s">
+        <v>500</v>
+      </c>
+      <c r="C252" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3">
+      <c r="B253" t="s">
+        <v>502</v>
+      </c>
+      <c r="C253" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3">
+      <c r="B254" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C254" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3">
+      <c r="B255" t="s">
+        <v>506</v>
+      </c>
+      <c r="C255" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3">
+      <c r="B256" t="s">
+        <v>508</v>
+      </c>
+      <c r="C256" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3">
+      <c r="B257" t="s">
+        <v>510</v>
+      </c>
+      <c r="C257" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3">
+      <c r="B258" t="s">
+        <v>512</v>
+      </c>
+      <c r="C258" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3">
+      <c r="B259" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3">
+      <c r="B260" t="s">
+        <v>516</v>
+      </c>
+      <c r="C260" t="s">
+        <v>517</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="B1:C259">
+    <sortCondition ref="B1"/>
+  </sortState>
   <conditionalFormatting sqref="B138">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -4135,7 +4898,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="B1:B137 B139:B153 B155:B1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="B1:B137 B139:B153 B155:B216 B218:B221 B225:B226 B228:B243 B245:B1048576" errorStyle="warning">
       <formula1>COUNTIF($B:$B,B1)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
